--- a/reports/portfolio-2025-04-26.xlsx
+++ b/reports/portfolio-2025-04-26.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\renanmogo\mfin-portfolio-management\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB43366A-1176-4418-AD1F-B57580C90BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373B1C8A-2AB8-40C8-8253-16F48410B5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9435" yWindow="1995" windowWidth="38700" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17625" yWindow="3285" windowWidth="33675" windowHeight="15345" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Portfolio Allocation" sheetId="1" r:id="rId1"/>
-    <sheet name="Daily Prices" sheetId="2" r:id="rId2"/>
-    <sheet name="Monthly Prices" sheetId="3" r:id="rId3"/>
-    <sheet name="Bond ETFs" sheetId="8" r:id="rId4"/>
-    <sheet name="Benchmark Stats" sheetId="5" r:id="rId5"/>
+    <sheet name="equity" sheetId="1" r:id="rId1"/>
+    <sheet name="daily_quotes" sheetId="2" r:id="rId2"/>
+    <sheet name="monthly_quotes" sheetId="3" r:id="rId3"/>
+    <sheet name="bond" sheetId="8" r:id="rId4"/>
+    <sheet name="benchmark" sheetId="5" r:id="rId5"/>
+    <sheet name="risk_free" sheetId="10" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Portfolio Allocation'!$A$1:$BC$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">equity!$A$1:$BC$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="186">
   <si>
     <t>Ticker</t>
   </si>
@@ -265,12 +266,6 @@
   </si>
   <si>
     <t>ADME</t>
-  </si>
-  <si>
-    <t>benchmark</t>
-  </si>
-  <si>
-    <t>stock</t>
   </si>
   <si>
     <t>intercept (alpha)</t>
@@ -595,6 +590,15 @@
   </si>
   <si>
     <t>^IRX</t>
+  </si>
+  <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
+    <t>Equity</t>
+  </si>
+  <si>
+    <t>Close</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1049,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -1204,13 +1208,13 @@
         <v>1</v>
       </c>
       <c r="BD1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="BF1" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:58" x14ac:dyDescent="0.25">
@@ -1218,7 +1222,7 @@
         <v>54</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
         <v>55</v>
@@ -1388,7 +1392,7 @@
         <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
         <v>62</v>
@@ -1564,22 +1568,22 @@
         <v>67</v>
       </c>
       <c r="B4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" t="s">
         <v>93</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>94</v>
-      </c>
-      <c r="D4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E4" t="s">
-        <v>96</v>
       </c>
       <c r="F4" t="s">
         <v>58</v>
       </c>
       <c r="G4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H4">
         <v>792728174592</v>
@@ -1740,7 +1744,7 @@
         <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
         <v>69</v>
@@ -1916,22 +1920,22 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
         <v>98</v>
-      </c>
-      <c r="D6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" t="s">
-        <v>100</v>
       </c>
       <c r="F6" t="s">
         <v>58</v>
       </c>
       <c r="G6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H6">
         <v>2984247296000</v>
@@ -2121,10 +2125,10 @@
         <v>73</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>74</v>
@@ -38550,10 +38554,10 @@
         <v>73</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>74</v>
@@ -40314,99 +40318,99 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" t="s">
         <v>123</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>124</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>125</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>126</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>127</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>128</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>129</v>
-      </c>
-      <c r="I2" t="s">
-        <v>130</v>
-      </c>
-      <c r="J2" t="s">
-        <v>131</v>
       </c>
       <c r="K2">
         <v>47391043605</v>
@@ -40415,7 +40419,7 @@
         <v>239454</v>
       </c>
       <c r="M2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N2">
         <v>4.9000000000000002E-2</v>
@@ -40447,34 +40451,34 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" t="s">
         <v>133</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>134</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>135</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>136</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>137</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J3" t="s">
         <v>138</v>
-      </c>
-      <c r="H3" t="s">
-        <v>139</v>
-      </c>
-      <c r="I3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J3" t="s">
-        <v>140</v>
       </c>
       <c r="K3">
         <v>603662245</v>
@@ -40483,7 +40487,7 @@
         <v>239424</v>
       </c>
       <c r="M3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N3">
         <v>5.6000000000000001E-2</v>
@@ -40515,34 +40519,34 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" t="s">
         <v>142</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>143</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>144</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>145</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>146</v>
       </c>
-      <c r="G4" t="s">
-        <v>147</v>
-      </c>
-      <c r="H4" t="s">
-        <v>148</v>
-      </c>
       <c r="I4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K4">
         <v>2481882421</v>
@@ -40551,7 +40555,7 @@
         <v>239423</v>
       </c>
       <c r="M4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="N4">
         <v>0.06</v>
@@ -40583,34 +40587,34 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" t="s">
         <v>150</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>151</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>152</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>153</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>154</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
+        <v>128</v>
+      </c>
+      <c r="J5" t="s">
         <v>155</v>
-      </c>
-      <c r="H5" t="s">
-        <v>156</v>
-      </c>
-      <c r="I5" t="s">
-        <v>130</v>
-      </c>
-      <c r="J5" t="s">
-        <v>157</v>
       </c>
       <c r="K5">
         <v>10058550338</v>
@@ -40619,7 +40623,7 @@
         <v>239453</v>
       </c>
       <c r="M5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="N5">
         <v>4.8000000000000001E-2</v>
@@ -40651,34 +40655,34 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" t="s">
         <v>159</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>160</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>161</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>162</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>163</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
+        <v>128</v>
+      </c>
+      <c r="J6" t="s">
         <v>164</v>
-      </c>
-      <c r="H6" t="s">
-        <v>165</v>
-      </c>
-      <c r="I6" t="s">
-        <v>130</v>
-      </c>
-      <c r="J6" t="s">
-        <v>166</v>
       </c>
       <c r="K6">
         <v>920048018</v>
@@ -40687,7 +40691,7 @@
         <v>239830</v>
       </c>
       <c r="M6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="N6">
         <v>2.8000000000000001E-2</v>
@@ -40719,34 +40723,34 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D7" t="s">
         <v>168</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>169</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>170</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>171</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>172</v>
       </c>
-      <c r="G7" t="s">
-        <v>173</v>
-      </c>
-      <c r="H7" t="s">
-        <v>174</v>
-      </c>
       <c r="I7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K7">
         <v>28645806282</v>
@@ -40755,7 +40759,7 @@
         <v>239566</v>
       </c>
       <c r="M7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N7">
         <v>5.3999999999999999E-2</v>
@@ -40787,34 +40791,34 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D8" t="s">
         <v>176</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>177</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>178</v>
-      </c>
-      <c r="E8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F8" t="s">
-        <v>180</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J8" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="K8">
         <v>89982204</v>
@@ -40823,7 +40827,7 @@
         <v>294319</v>
       </c>
       <c r="M8" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N8">
         <v>5.1999999999999998E-2</v>
@@ -40873,28 +40877,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -41025,6 +41029,41 @@
       </c>
       <c r="H6">
         <v>0.1203577206530437</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EDEF7A0-4AA8-410D-B1C0-A2F348898CFF}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>45772</v>
+      </c>
+      <c r="B2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2">
+        <v>4.1900000000000004</v>
       </c>
     </row>
   </sheetData>

--- a/reports/portfolio-2025-04-26.xlsx
+++ b/reports/portfolio-2025-04-26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\renanmogo\mfin-portfolio-management\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{373B1C8A-2AB8-40C8-8253-16F48410B5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17790106-85A2-4DC1-A7A1-F6D537A5E352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17625" yWindow="3285" windowWidth="33675" windowHeight="15345" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13050" yWindow="3630" windowWidth="33675" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="equity" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="185">
   <si>
     <t>Ticker</t>
   </si>
@@ -394,12 +394,6 @@
     <t>Duration (D*)</t>
   </si>
   <si>
-    <t>Price Change Sensitivity</t>
-  </si>
-  <si>
-    <t>Expected_Return</t>
-  </si>
-  <si>
     <t>Standard_Deviation</t>
   </si>
   <si>
@@ -599,6 +593,9 @@
   </si>
   <si>
     <t>Close</t>
+  </si>
+  <si>
+    <t>Price Change Sensitivity (Expected Return)</t>
   </si>
 </sst>
 </file>
@@ -2125,7 +2122,7 @@
         <v>73</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>81</v>
@@ -38554,7 +38551,7 @@
         <v>73</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>81</v>
@@ -40310,10 +40307,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82089530-D438-45CC-889A-85BEC0FB44C3}">
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -40369,48 +40366,45 @@
         <v>116</v>
       </c>
       <c r="S1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" t="s">
         <v>121</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>122</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>123</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>124</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>125</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>126</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>127</v>
-      </c>
-      <c r="I2" t="s">
-        <v>128</v>
-      </c>
-      <c r="J2" t="s">
-        <v>129</v>
       </c>
       <c r="K2">
         <v>47391043605</v>
@@ -40419,7 +40413,7 @@
         <v>239454</v>
       </c>
       <c r="M2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N2">
         <v>4.9000000000000002E-2</v>
@@ -40440,45 +40434,42 @@
         <v>0.18160000000000001</v>
       </c>
       <c r="T2">
-        <v>-0.1044389808828483</v>
+        <v>0.16275201771808359</v>
       </c>
       <c r="U2">
-        <v>0.16275201771808359</v>
-      </c>
-      <c r="V2">
         <v>-0.9077551415599614</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" t="s">
         <v>131</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>132</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>133</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>134</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>135</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J3" t="s">
         <v>136</v>
-      </c>
-      <c r="H3" t="s">
-        <v>137</v>
-      </c>
-      <c r="I3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J3" t="s">
-        <v>138</v>
       </c>
       <c r="K3">
         <v>603662245</v>
@@ -40487,7 +40478,7 @@
         <v>239424</v>
       </c>
       <c r="M3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N3">
         <v>5.6000000000000001E-2</v>
@@ -40508,45 +40499,42 @@
         <v>0.14899999999999999</v>
       </c>
       <c r="T3">
-        <v>-4.5010582848321712E-2</v>
+        <v>0.12820402798735631</v>
       </c>
       <c r="U3">
-        <v>0.12820402798735631</v>
-      </c>
-      <c r="V3">
         <v>-0.68882845753513322</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" t="s">
         <v>140</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>141</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>142</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>143</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>144</v>
       </c>
-      <c r="G4" t="s">
-        <v>145</v>
-      </c>
-      <c r="H4" t="s">
-        <v>146</v>
-      </c>
       <c r="I4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K4">
         <v>2481882421</v>
@@ -40555,7 +40543,7 @@
         <v>239423</v>
       </c>
       <c r="M4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N4">
         <v>0.06</v>
@@ -40576,45 +40564,42 @@
         <v>0.14599999999999999</v>
       </c>
       <c r="T4">
-        <v>-2.4845237645077959E-2</v>
+        <v>0.12709259199824521</v>
       </c>
       <c r="U4">
-        <v>0.12709259199824521</v>
-      </c>
-      <c r="V4">
         <v>-0.53618575696385873</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5" t="s">
         <v>148</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>149</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>150</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>151</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>152</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J5" t="s">
         <v>153</v>
-      </c>
-      <c r="H5" t="s">
-        <v>154</v>
-      </c>
-      <c r="I5" t="s">
-        <v>128</v>
-      </c>
-      <c r="J5" t="s">
-        <v>155</v>
       </c>
       <c r="K5">
         <v>10058550338</v>
@@ -40623,7 +40608,7 @@
         <v>239453</v>
       </c>
       <c r="M5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N5">
         <v>4.8000000000000001E-2</v>
@@ -40644,45 +40629,42 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="T5">
-        <v>-7.5626042566015239E-2</v>
+        <v>0.1286951734392113</v>
       </c>
       <c r="U5">
-        <v>0.1286951734392113</v>
-      </c>
-      <c r="V5">
         <v>-0.9240909304356274</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" t="s">
         <v>157</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>158</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>159</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>160</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>161</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
+        <v>126</v>
+      </c>
+      <c r="J6" t="s">
         <v>162</v>
-      </c>
-      <c r="H6" t="s">
-        <v>163</v>
-      </c>
-      <c r="I6" t="s">
-        <v>128</v>
-      </c>
-      <c r="J6" t="s">
-        <v>164</v>
       </c>
       <c r="K6">
         <v>920048018</v>
@@ -40691,7 +40673,7 @@
         <v>239830</v>
       </c>
       <c r="M6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N6">
         <v>2.8000000000000001E-2</v>
@@ -40712,45 +40694,42 @@
         <v>8.5400000000000004E-2</v>
       </c>
       <c r="T6">
-        <v>-3.4969960724967719E-2</v>
+        <v>9.5426275485568091E-2</v>
       </c>
       <c r="U6">
-        <v>9.5426275485568091E-2</v>
-      </c>
-      <c r="V6">
         <v>-0.82021393297284229</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" t="s">
         <v>166</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>167</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>168</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>169</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>170</v>
       </c>
-      <c r="G7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" t="s">
-        <v>172</v>
-      </c>
       <c r="I7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K7">
         <v>28645806282</v>
@@ -40759,7 +40738,7 @@
         <v>239566</v>
       </c>
       <c r="M7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N7">
         <v>5.3999999999999999E-2</v>
@@ -40780,45 +40759,42 @@
         <v>9.7500000000000003E-2</v>
       </c>
       <c r="T7">
-        <v>-4.0814861551492498E-3</v>
+        <v>8.7959635988240803E-2</v>
       </c>
       <c r="U7">
-        <v>8.7959635988240803E-2</v>
-      </c>
-      <c r="V7">
         <v>-0.53867305864571347</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" t="s">
         <v>174</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>175</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>176</v>
-      </c>
-      <c r="E8" t="s">
-        <v>177</v>
-      </c>
-      <c r="F8" t="s">
-        <v>178</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J8" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="K8">
         <v>89982204</v>
@@ -40827,7 +40803,7 @@
         <v>294319</v>
       </c>
       <c r="M8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="N8">
         <v>5.1999999999999998E-2</v>
@@ -40848,12 +40824,9 @@
         <v>0.1169</v>
       </c>
       <c r="T8">
-        <v>3.7107882434858068E-2</v>
+        <v>8.8501290062151808E-2</v>
       </c>
       <c r="U8">
-        <v>8.8501290062151808E-2</v>
-      </c>
-      <c r="V8">
         <v>-6.996641021609272E-2</v>
       </c>
     </row>
@@ -40877,10 +40850,10 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>75</v>
@@ -41052,7 +41025,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -41060,7 +41033,7 @@
         <v>45772</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C2">
         <v>4.1900000000000004</v>
